--- a/Klasifikasi/aspect_sentiment_summary.xlsx
+++ b/Klasifikasi/aspect_sentiment_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -515,6 +515,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Verifikasi Usia</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Klasifikasi/aspect_sentiment_summary.xlsx
+++ b/Klasifikasi/aspect_sentiment_summary.xlsx
@@ -441,30 +441,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Konten Negatif</t>
+          <t>Kecanduan</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kecanduan</t>
+          <t>Konten Negatif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
         <v>25</v>
@@ -473,33 +473,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pengawasan Orang Tua</t>
+          <t>Batas Usia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Batas Usia</t>
+          <t>Pengawasan Orang Tua</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
